--- a/DSA for PLACEMENTS 1.xlsx
+++ b/DSA for PLACEMENTS 1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9765abdd1e291f17/Desktop/DSA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="11_2E2C462B86E80A008A522AE716C952C441A6BCAD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BF0B0198-F4D4-4734-B053-4172BD69A94A}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="11_2E2C462B86E80A008A522AE716C952C441A6BCAD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B004C84D-FC14-48E7-A0E3-EFE78325CDA3}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="853" uniqueCount="420">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="856" uniqueCount="421">
   <si>
     <t>Do NOT send any edit request to this sheet. Instead, make a copy of your own.</t>
   </si>
@@ -1302,6 +1302,9 @@
   </si>
   <si>
     <t>Done</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Done </t>
   </si>
 </sst>
 </file>
@@ -1529,24 +1532,24 @@
     <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1783,11 +1786,11 @@
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="2"/>
-      <c r="D1" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
+      <c r="D1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
       <c r="G1" s="3"/>
       <c r="H1" s="21"/>
       <c r="I1" s="3"/>
@@ -1799,13 +1802,13 @@
       <c r="D2" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
       <c r="G2" s="3"/>
       <c r="H2" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="27"/>
+      <c r="I2" s="29"/>
     </row>
     <row r="3" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
@@ -1842,7 +1845,7 @@
       <c r="I4" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="J4" s="32" t="s">
+      <c r="J4" s="26" t="s">
         <v>418</v>
       </c>
     </row>
@@ -1858,7 +1861,7 @@
       <c r="I5" s="3"/>
     </row>
     <row r="6" spans="1:10" ht="14.5" x14ac:dyDescent="0.4">
-      <c r="A6" s="26" t="s">
+      <c r="A6" s="32" t="s">
         <v>10</v>
       </c>
       <c r="B6" s="3" t="b">
@@ -1883,12 +1886,12 @@
         <v>15</v>
       </c>
       <c r="I6" s="3"/>
-      <c r="J6" s="33" t="s">
+      <c r="J6" s="27" t="s">
         <v>419</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="14.5" x14ac:dyDescent="0.4">
-      <c r="A7" s="27"/>
+      <c r="A7" s="29"/>
       <c r="B7" s="3" t="b">
         <v>0</v>
       </c>
@@ -1913,12 +1916,12 @@
       <c r="I7" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="J7" s="33" t="s">
+      <c r="J7" s="27" t="s">
         <v>419</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="14.5" x14ac:dyDescent="0.4">
-      <c r="A8" s="27"/>
+      <c r="A8" s="29"/>
       <c r="B8" s="3" t="b">
         <v>0</v>
       </c>
@@ -1943,12 +1946,12 @@
       <c r="I8" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="J8" s="33" t="s">
+      <c r="J8" s="27" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A9" s="27"/>
+    <row r="9" spans="1:10" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A9" s="29"/>
       <c r="B9" s="3" t="b">
         <v>0</v>
       </c>
@@ -1969,9 +1972,12 @@
       </c>
       <c r="H9" s="9"/>
       <c r="I9" s="3"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A10" s="27"/>
+      <c r="J9" s="1" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A10" s="29"/>
       <c r="B10" s="3" t="b">
         <v>0</v>
       </c>
@@ -1994,9 +2000,12 @@
         <v>24</v>
       </c>
       <c r="I10" s="3"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A11" s="27"/>
+      <c r="J10" s="1" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A11" s="29"/>
       <c r="B11" s="1"/>
       <c r="C11" s="2"/>
       <c r="D11" s="1"/>
@@ -2006,8 +2015,8 @@
       <c r="H11" s="9"/>
       <c r="I11" s="3"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A12" s="27"/>
+    <row r="12" spans="1:10" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A12" s="29"/>
       <c r="B12" s="3" t="b">
         <v>0</v>
       </c>
@@ -2030,9 +2039,12 @@
         <v>27</v>
       </c>
       <c r="I12" s="3"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A13" s="27"/>
+      <c r="J12" s="1" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A13" s="29"/>
       <c r="B13" s="3" t="b">
         <v>0</v>
       </c>
@@ -2054,8 +2066,8 @@
       <c r="H13" s="9"/>
       <c r="I13" s="3"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A14" s="27"/>
+    <row r="14" spans="1:10" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A14" s="29"/>
       <c r="B14" s="3" t="b">
         <v>0</v>
       </c>
@@ -2079,8 +2091,8 @@
       </c>
       <c r="I14" s="3"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A15" s="27"/>
+    <row r="15" spans="1:10" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A15" s="29"/>
       <c r="B15" s="3" t="b">
         <v>0</v>
       </c>
@@ -2106,8 +2118,8 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="13" x14ac:dyDescent="0.3">
-      <c r="A16" s="27"/>
+    <row r="16" spans="1:10" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A16" s="29"/>
       <c r="B16" s="3" t="b">
         <v>0</v>
       </c>
@@ -2133,8 +2145,8 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A17" s="27"/>
+    <row r="17" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A17" s="29"/>
       <c r="B17" s="3" t="b">
         <v>0</v>
       </c>
@@ -2158,8 +2170,8 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A18" s="27"/>
+    <row r="18" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A18" s="29"/>
       <c r="B18" s="3" t="b">
         <v>0</v>
       </c>
@@ -2183,8 +2195,8 @@
         <v>37</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A19" s="27"/>
+    <row r="19" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A19" s="29"/>
       <c r="B19" s="3" t="b">
         <v>0</v>
       </c>
@@ -2210,8 +2222,8 @@
         <v>21</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A20" s="27"/>
+    <row r="20" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A20" s="29"/>
       <c r="B20" s="3" t="b">
         <v>0</v>
       </c>
@@ -2235,8 +2247,8 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A21" s="27"/>
+    <row r="21" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A21" s="29"/>
       <c r="B21" s="3" t="b">
         <v>0</v>
       </c>
@@ -2260,8 +2272,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A22" s="27"/>
+    <row r="22" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A22" s="29"/>
       <c r="B22" s="3" t="b">
         <v>0</v>
       </c>
@@ -2285,8 +2297,8 @@
         <v>47</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A23" s="27"/>
+    <row r="23" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A23" s="29"/>
       <c r="B23" s="3" t="b">
         <v>0</v>
       </c>
@@ -2310,8 +2322,8 @@
         <v>50</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A24" s="27"/>
+    <row r="24" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A24" s="29"/>
       <c r="B24" s="3" t="b">
         <v>0</v>
       </c>
@@ -2335,8 +2347,8 @@
       </c>
       <c r="I24" s="3"/>
     </row>
-    <row r="25" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A25" s="27"/>
+    <row r="25" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A25" s="29"/>
       <c r="B25" s="3" t="b">
         <v>0</v>
       </c>
@@ -2358,8 +2370,8 @@
         <v>18</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A26" s="27"/>
+    <row r="26" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A26" s="29"/>
       <c r="B26" s="3" t="b">
         <v>0</v>
       </c>
@@ -2385,8 +2397,8 @@
         <v>56</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A27" s="27"/>
+    <row r="27" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A27" s="29"/>
       <c r="B27" s="3"/>
       <c r="C27" s="2"/>
       <c r="D27" s="1"/>
@@ -2396,8 +2408,8 @@
       <c r="H27" s="9"/>
       <c r="I27" s="3"/>
     </row>
-    <row r="28" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A28" s="27"/>
+    <row r="28" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A28" s="29"/>
       <c r="B28" s="3" t="b">
         <v>0</v>
       </c>
@@ -2421,8 +2433,8 @@
         <v>60</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A29" s="27"/>
+    <row r="29" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A29" s="29"/>
       <c r="B29" s="3" t="b">
         <v>0</v>
       </c>
@@ -2446,8 +2458,8 @@
       </c>
       <c r="I29" s="3"/>
     </row>
-    <row r="30" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A30" s="27"/>
+    <row r="30" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A30" s="29"/>
       <c r="B30" s="3" t="b">
         <v>0</v>
       </c>
@@ -2473,8 +2485,8 @@
         <v>18</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A31" s="27"/>
+    <row r="31" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A31" s="29"/>
       <c r="B31" s="3" t="b">
         <v>0</v>
       </c>
@@ -2496,8 +2508,8 @@
         <v>60</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A32" s="27"/>
+    <row r="32" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A32" s="29"/>
       <c r="B32" s="3" t="b">
         <v>0</v>
       </c>
@@ -2519,7 +2531,7 @@
       <c r="H32" s="9"/>
       <c r="I32" s="3"/>
     </row>
-    <row r="33" spans="1:9" ht="13" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="2"/>
@@ -2530,7 +2542,7 @@
       <c r="H33" s="9"/>
       <c r="I33" s="3"/>
     </row>
-    <row r="34" spans="1:9" ht="13" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="2"/>
@@ -2541,8 +2553,8 @@
       <c r="H34" s="9"/>
       <c r="I34" s="3"/>
     </row>
-    <row r="35" spans="1:9" ht="14" x14ac:dyDescent="0.3">
-      <c r="A35" s="28" t="s">
+    <row r="35" spans="1:9" ht="15" x14ac:dyDescent="0.4">
+      <c r="A35" s="33" t="s">
         <v>68</v>
       </c>
       <c r="B35" s="3" t="b">
@@ -2569,7 +2581,7 @@
       <c r="I35" s="3"/>
     </row>
     <row r="36" spans="1:9" ht="14" x14ac:dyDescent="0.3">
-      <c r="A36" s="27"/>
+      <c r="A36" s="29"/>
       <c r="B36" s="3" t="b">
         <v>0</v>
       </c>
@@ -2591,8 +2603,8 @@
       <c r="H36" s="17"/>
       <c r="I36" s="18"/>
     </row>
-    <row r="37" spans="1:9" ht="14" x14ac:dyDescent="0.3">
-      <c r="A37" s="27"/>
+    <row r="37" spans="1:9" ht="15" x14ac:dyDescent="0.4">
+      <c r="A37" s="29"/>
       <c r="B37" s="3" t="b">
         <v>0</v>
       </c>
@@ -2614,8 +2626,8 @@
       <c r="H37" s="9"/>
       <c r="I37" s="3"/>
     </row>
-    <row r="38" spans="1:9" ht="14" x14ac:dyDescent="0.3">
-      <c r="A38" s="27"/>
+    <row r="38" spans="1:9" ht="15" x14ac:dyDescent="0.4">
+      <c r="A38" s="29"/>
       <c r="B38" s="3" t="b">
         <v>0</v>
       </c>
@@ -2640,7 +2652,7 @@
       <c r="I38" s="3"/>
     </row>
     <row r="39" spans="1:9" ht="14" x14ac:dyDescent="0.3">
-      <c r="A39" s="27"/>
+      <c r="A39" s="29"/>
       <c r="B39" s="3" t="b">
         <v>0</v>
       </c>
@@ -2662,8 +2674,8 @@
       <c r="H39" s="17"/>
       <c r="I39" s="3"/>
     </row>
-    <row r="40" spans="1:9" ht="14" x14ac:dyDescent="0.3">
-      <c r="A40" s="27"/>
+    <row r="40" spans="1:9" ht="15" x14ac:dyDescent="0.4">
+      <c r="A40" s="29"/>
       <c r="B40" s="3" t="b">
         <v>0</v>
       </c>
@@ -2687,8 +2699,8 @@
       </c>
       <c r="I40" s="3"/>
     </row>
-    <row r="41" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A41" s="27"/>
+    <row r="41" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A41" s="29"/>
       <c r="B41" s="3" t="b">
         <v>0</v>
       </c>
@@ -2710,7 +2722,7 @@
       </c>
       <c r="I41" s="3"/>
     </row>
-    <row r="42" spans="1:9" ht="13" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="2"/>
@@ -2732,8 +2744,8 @@
       <c r="H43" s="21"/>
       <c r="I43" s="3"/>
     </row>
-    <row r="44" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A44" s="26" t="s">
+    <row r="44" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A44" s="32" t="s">
         <v>80</v>
       </c>
       <c r="B44" s="3" t="b">
@@ -2759,8 +2771,8 @@
       </c>
       <c r="I44" s="3"/>
     </row>
-    <row r="45" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A45" s="27"/>
+    <row r="45" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A45" s="29"/>
       <c r="B45" s="3" t="b">
         <v>0</v>
       </c>
@@ -2782,8 +2794,8 @@
       </c>
       <c r="I45" s="3"/>
     </row>
-    <row r="46" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A46" s="27"/>
+    <row r="46" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A46" s="29"/>
       <c r="B46" s="3" t="b">
         <v>0</v>
       </c>
@@ -2806,7 +2818,7 @@
       <c r="I46" s="3"/>
     </row>
     <row r="47" spans="1:9" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A47" s="27"/>
+      <c r="A47" s="29"/>
       <c r="B47" s="3" t="b">
         <v>0</v>
       </c>
@@ -2829,7 +2841,7 @@
       <c r="I47" s="3"/>
     </row>
     <row r="48" spans="1:9" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A48" s="27"/>
+      <c r="A48" s="29"/>
       <c r="B48" s="3" t="b">
         <v>0</v>
       </c>
@@ -2852,7 +2864,7 @@
       <c r="I48" s="3"/>
     </row>
     <row r="49" spans="1:9" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A49" s="27"/>
+      <c r="A49" s="29"/>
       <c r="B49" s="3" t="b">
         <v>0</v>
       </c>
@@ -2877,7 +2889,7 @@
       <c r="I49" s="3"/>
     </row>
     <row r="50" spans="1:9" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A50" s="27"/>
+      <c r="A50" s="29"/>
       <c r="B50" s="3" t="b">
         <v>0</v>
       </c>
@@ -2900,7 +2912,7 @@
       <c r="I50" s="3"/>
     </row>
     <row r="51" spans="1:9" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A51" s="27"/>
+      <c r="A51" s="29"/>
       <c r="B51" s="3" t="b">
         <v>0</v>
       </c>
@@ -2922,8 +2934,8 @@
       </c>
       <c r="I51" s="3"/>
     </row>
-    <row r="52" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A52" s="27"/>
+    <row r="52" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A52" s="29"/>
       <c r="B52" s="3" t="b">
         <v>0</v>
       </c>
@@ -2946,7 +2958,7 @@
       <c r="I52" s="3"/>
     </row>
     <row r="53" spans="1:9" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A53" s="27"/>
+      <c r="A53" s="29"/>
       <c r="B53" s="3" t="b">
         <v>0</v>
       </c>
@@ -2967,7 +2979,7 @@
       <c r="I53" s="3"/>
     </row>
     <row r="54" spans="1:9" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A54" s="27"/>
+      <c r="A54" s="29"/>
       <c r="B54" s="3" t="b">
         <v>0</v>
       </c>
@@ -3005,8 +3017,8 @@
       <c r="H56" s="21"/>
       <c r="I56" s="3"/>
     </row>
-    <row r="57" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A57" s="28" t="s">
+    <row r="57" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A57" s="33" t="s">
         <v>98</v>
       </c>
       <c r="B57" s="3" t="b">
@@ -3032,8 +3044,8 @@
       </c>
       <c r="I57" s="3"/>
     </row>
-    <row r="58" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A58" s="27"/>
+    <row r="58" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A58" s="29"/>
       <c r="B58" s="3" t="b">
         <v>0</v>
       </c>
@@ -3055,8 +3067,8 @@
       </c>
       <c r="I58" s="3"/>
     </row>
-    <row r="59" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A59" s="27"/>
+    <row r="59" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A59" s="29"/>
       <c r="B59" s="3" t="b">
         <v>0</v>
       </c>
@@ -3080,8 +3092,8 @@
       </c>
       <c r="I59" s="3"/>
     </row>
-    <row r="60" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A60" s="27"/>
+    <row r="60" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A60" s="29"/>
       <c r="B60" s="3" t="b">
         <v>0</v>
       </c>
@@ -3103,8 +3115,8 @@
       </c>
       <c r="I60" s="3"/>
     </row>
-    <row r="61" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A61" s="27"/>
+    <row r="61" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A61" s="29"/>
       <c r="B61" s="3" t="b">
         <v>0</v>
       </c>
@@ -3126,8 +3138,8 @@
       </c>
       <c r="I61" s="3"/>
     </row>
-    <row r="62" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A62" s="27"/>
+    <row r="62" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A62" s="29"/>
       <c r="B62" s="3" t="b">
         <v>0</v>
       </c>
@@ -3152,7 +3164,7 @@
       <c r="I62" s="3"/>
     </row>
     <row r="63" spans="1:9" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A63" s="27"/>
+      <c r="A63" s="29"/>
       <c r="B63" s="3" t="b">
         <v>0</v>
       </c>
@@ -3176,8 +3188,8 @@
       </c>
       <c r="I63" s="3"/>
     </row>
-    <row r="64" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A64" s="27"/>
+    <row r="64" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A64" s="29"/>
       <c r="B64" s="3" t="b">
         <v>0</v>
       </c>
@@ -3199,8 +3211,8 @@
       </c>
       <c r="I64" s="3"/>
     </row>
-    <row r="65" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A65" s="27"/>
+    <row r="65" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A65" s="29"/>
       <c r="B65" s="3" t="b">
         <v>0</v>
       </c>
@@ -3225,7 +3237,7 @@
       <c r="I65" s="3"/>
     </row>
     <row r="66" spans="1:9" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A66" s="27"/>
+      <c r="A66" s="29"/>
       <c r="B66" s="3" t="b">
         <v>0</v>
       </c>
@@ -3250,7 +3262,7 @@
       <c r="I66" s="3"/>
     </row>
     <row r="67" spans="1:9" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A67" s="27"/>
+      <c r="A67" s="29"/>
       <c r="B67" s="3" t="b">
         <v>0</v>
       </c>
@@ -3294,8 +3306,8 @@
       <c r="H69" s="21"/>
       <c r="I69" s="3"/>
     </row>
-    <row r="70" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A70" s="28" t="s">
+    <row r="70" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A70" s="33" t="s">
         <v>118</v>
       </c>
       <c r="B70" s="3" t="b">
@@ -3321,8 +3333,8 @@
       </c>
       <c r="I70" s="3"/>
     </row>
-    <row r="71" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A71" s="27"/>
+    <row r="71" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A71" s="29"/>
       <c r="B71" s="3" t="b">
         <v>0</v>
       </c>
@@ -3346,8 +3358,8 @@
       </c>
       <c r="I71" s="3"/>
     </row>
-    <row r="72" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A72" s="27"/>
+    <row r="72" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A72" s="29"/>
       <c r="B72" s="3" t="b">
         <v>0</v>
       </c>
@@ -3371,8 +3383,8 @@
       </c>
       <c r="I72" s="3"/>
     </row>
-    <row r="73" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A73" s="27"/>
+    <row r="73" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A73" s="29"/>
       <c r="B73" s="3" t="b">
         <v>0</v>
       </c>
@@ -3394,8 +3406,8 @@
       </c>
       <c r="I73" s="3"/>
     </row>
-    <row r="74" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A74" s="27"/>
+    <row r="74" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A74" s="29"/>
       <c r="B74" s="3" t="b">
         <v>0</v>
       </c>
@@ -3419,8 +3431,8 @@
       </c>
       <c r="I74" s="3"/>
     </row>
-    <row r="75" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A75" s="27"/>
+    <row r="75" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A75" s="29"/>
       <c r="B75" s="3" t="b">
         <v>0</v>
       </c>
@@ -3445,7 +3457,7 @@
       <c r="I75" s="3"/>
     </row>
     <row r="76" spans="1:9" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A76" s="27"/>
+      <c r="A76" s="29"/>
       <c r="B76" s="3" t="b">
         <v>0</v>
       </c>
@@ -3469,8 +3481,8 @@
       </c>
       <c r="I76" s="3"/>
     </row>
-    <row r="77" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A77" s="27"/>
+    <row r="77" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A77" s="29"/>
       <c r="B77" s="3" t="b">
         <v>0</v>
       </c>
@@ -3495,7 +3507,7 @@
       <c r="I77" s="3"/>
     </row>
     <row r="78" spans="1:9" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A78" s="27"/>
+      <c r="A78" s="29"/>
       <c r="B78" s="3" t="b">
         <v>0</v>
       </c>
@@ -3517,8 +3529,8 @@
       </c>
       <c r="I78" s="3"/>
     </row>
-    <row r="79" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A79" s="27"/>
+    <row r="79" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A79" s="29"/>
       <c r="B79" s="3" t="b">
         <v>0</v>
       </c>
@@ -3541,7 +3553,7 @@
       <c r="I79" s="3"/>
     </row>
     <row r="80" spans="1:9" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A80" s="27"/>
+      <c r="A80" s="29"/>
       <c r="B80" s="3" t="b">
         <v>0</v>
       </c>
@@ -3566,7 +3578,7 @@
       <c r="I80" s="3"/>
     </row>
     <row r="81" spans="1:9" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A81" s="27"/>
+      <c r="A81" s="29"/>
       <c r="B81" s="3" t="b">
         <v>0</v>
       </c>
@@ -3589,7 +3601,7 @@
       <c r="I81" s="3"/>
     </row>
     <row r="82" spans="1:9" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A82" s="27"/>
+      <c r="A82" s="29"/>
       <c r="B82" s="3" t="b">
         <v>0</v>
       </c>
@@ -3635,8 +3647,8 @@
       <c r="H84" s="21"/>
       <c r="I84" s="3"/>
     </row>
-    <row r="85" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A85" s="26" t="s">
+    <row r="85" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A85" s="32" t="s">
         <v>145</v>
       </c>
       <c r="B85" s="3" t="b">
@@ -3663,7 +3675,7 @@
       <c r="I85" s="3"/>
     </row>
     <row r="86" spans="1:9" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A86" s="27"/>
+      <c r="A86" s="29"/>
       <c r="B86" s="3" t="b">
         <v>0</v>
       </c>
@@ -3687,8 +3699,8 @@
       </c>
       <c r="I86" s="3"/>
     </row>
-    <row r="87" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A87" s="27"/>
+    <row r="87" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A87" s="29"/>
       <c r="B87" s="3" t="b">
         <v>0</v>
       </c>
@@ -3712,8 +3724,8 @@
       </c>
       <c r="I87" s="3"/>
     </row>
-    <row r="88" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A88" s="27"/>
+    <row r="88" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A88" s="29"/>
       <c r="B88" s="3" t="b">
         <v>0</v>
       </c>
@@ -3737,8 +3749,8 @@
       </c>
       <c r="I88" s="3"/>
     </row>
-    <row r="89" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A89" s="27"/>
+    <row r="89" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A89" s="29"/>
       <c r="B89" s="3" t="b">
         <v>0</v>
       </c>
@@ -3762,8 +3774,8 @@
       </c>
       <c r="I89" s="3"/>
     </row>
-    <row r="90" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A90" s="27"/>
+    <row r="90" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A90" s="29"/>
       <c r="B90" s="3" t="b">
         <v>0</v>
       </c>
@@ -3786,7 +3798,7 @@
       <c r="I90" s="3"/>
     </row>
     <row r="91" spans="1:9" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A91" s="27"/>
+      <c r="A91" s="29"/>
       <c r="B91" s="3" t="b">
         <v>0</v>
       </c>
@@ -3808,8 +3820,8 @@
       </c>
       <c r="I91" s="3"/>
     </row>
-    <row r="92" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A92" s="27"/>
+    <row r="92" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A92" s="29"/>
       <c r="B92" s="3" t="b">
         <v>0</v>
       </c>
@@ -3833,8 +3845,8 @@
       </c>
       <c r="I92" s="3"/>
     </row>
-    <row r="93" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A93" s="27"/>
+    <row r="93" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A93" s="29"/>
       <c r="B93" s="3" t="b">
         <v>0</v>
       </c>
@@ -3858,8 +3870,8 @@
       </c>
       <c r="I93" s="3"/>
     </row>
-    <row r="94" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A94" s="27"/>
+    <row r="94" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A94" s="29"/>
       <c r="B94" s="3" t="b">
         <v>0</v>
       </c>
@@ -3884,7 +3896,7 @@
       <c r="I94" s="3"/>
     </row>
     <row r="95" spans="1:9" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A95" s="27"/>
+      <c r="A95" s="29"/>
       <c r="B95" s="3" t="b">
         <v>0</v>
       </c>
@@ -3908,8 +3920,8 @@
       </c>
       <c r="I95" s="3"/>
     </row>
-    <row r="96" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A96" s="27"/>
+    <row r="96" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A96" s="29"/>
       <c r="B96" s="3" t="b">
         <v>0</v>
       </c>
@@ -3933,8 +3945,8 @@
       </c>
       <c r="I96" s="3"/>
     </row>
-    <row r="97" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A97" s="27"/>
+    <row r="97" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A97" s="29"/>
       <c r="B97" s="3" t="b">
         <v>0</v>
       </c>
@@ -3956,8 +3968,8 @@
       </c>
       <c r="I97" s="3"/>
     </row>
-    <row r="98" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A98" s="27"/>
+    <row r="98" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A98" s="29"/>
       <c r="B98" s="3" t="b">
         <v>0</v>
       </c>
@@ -3982,7 +3994,7 @@
       <c r="I98" s="3"/>
     </row>
     <row r="99" spans="1:9" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A99" s="27"/>
+      <c r="A99" s="29"/>
       <c r="B99" s="3" t="b">
         <v>0</v>
       </c>
@@ -4029,7 +4041,7 @@
       <c r="I101" s="3"/>
     </row>
     <row r="102" spans="1:9" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A102" s="26" t="s">
+      <c r="A102" s="32" t="s">
         <v>176</v>
       </c>
       <c r="B102" s="3" t="b">
@@ -4056,7 +4068,7 @@
       <c r="I102" s="3"/>
     </row>
     <row r="103" spans="1:9" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A103" s="27"/>
+      <c r="A103" s="29"/>
       <c r="B103" s="3" t="b">
         <v>0</v>
       </c>
@@ -4081,7 +4093,7 @@
       <c r="I103" s="3"/>
     </row>
     <row r="104" spans="1:9" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A104" s="27"/>
+      <c r="A104" s="29"/>
       <c r="B104" s="3" t="b">
         <v>0</v>
       </c>
@@ -4105,8 +4117,8 @@
       </c>
       <c r="I104" s="3"/>
     </row>
-    <row r="105" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A105" s="27"/>
+    <row r="105" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A105" s="29"/>
       <c r="B105" s="3" t="b">
         <v>0</v>
       </c>
@@ -4129,7 +4141,7 @@
       <c r="I105" s="3"/>
     </row>
     <row r="106" spans="1:9" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A106" s="27"/>
+      <c r="A106" s="29"/>
       <c r="B106" s="3" t="b">
         <v>0</v>
       </c>
@@ -4153,8 +4165,8 @@
       </c>
       <c r="I106" s="3"/>
     </row>
-    <row r="107" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A107" s="27"/>
+    <row r="107" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A107" s="29"/>
       <c r="B107" s="3" t="b">
         <v>0</v>
       </c>
@@ -4179,7 +4191,7 @@
       <c r="I107" s="3"/>
     </row>
     <row r="108" spans="1:9" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A108" s="27"/>
+      <c r="A108" s="29"/>
       <c r="B108" s="3" t="b">
         <v>0</v>
       </c>
@@ -4204,7 +4216,7 @@
       <c r="I108" s="3"/>
     </row>
     <row r="109" spans="1:9" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A109" s="27"/>
+      <c r="A109" s="29"/>
       <c r="B109" s="3" t="b">
         <v>0</v>
       </c>
@@ -4228,8 +4240,8 @@
       </c>
       <c r="I109" s="3"/>
     </row>
-    <row r="110" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A110" s="27"/>
+    <row r="110" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A110" s="29"/>
       <c r="B110" s="3" t="b">
         <v>0</v>
       </c>
@@ -4251,8 +4263,8 @@
       </c>
       <c r="I110" s="3"/>
     </row>
-    <row r="111" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A111" s="27"/>
+    <row r="111" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A111" s="29"/>
       <c r="B111" s="3" t="b">
         <v>0</v>
       </c>
@@ -4276,8 +4288,8 @@
       </c>
       <c r="I111" s="3"/>
     </row>
-    <row r="112" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A112" s="27"/>
+    <row r="112" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A112" s="29"/>
       <c r="B112" s="3" t="b">
         <v>0</v>
       </c>
@@ -4299,8 +4311,8 @@
       </c>
       <c r="I112" s="3"/>
     </row>
-    <row r="113" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A113" s="27"/>
+    <row r="113" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A113" s="29"/>
       <c r="B113" s="3" t="b">
         <v>0</v>
       </c>
@@ -4324,8 +4336,8 @@
       </c>
       <c r="I113" s="3"/>
     </row>
-    <row r="114" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A114" s="27"/>
+    <row r="114" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A114" s="29"/>
       <c r="B114" s="3" t="b">
         <v>0</v>
       </c>
@@ -4347,8 +4359,8 @@
       </c>
       <c r="I114" s="3"/>
     </row>
-    <row r="115" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A115" s="27"/>
+    <row r="115" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A115" s="29"/>
       <c r="B115" s="3" t="b">
         <v>0</v>
       </c>
@@ -4370,8 +4382,8 @@
       </c>
       <c r="I115" s="3"/>
     </row>
-    <row r="116" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A116" s="27"/>
+    <row r="116" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A116" s="29"/>
       <c r="B116" s="3" t="b">
         <v>0</v>
       </c>
@@ -4395,8 +4407,8 @@
       </c>
       <c r="I116" s="3"/>
     </row>
-    <row r="117" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A117" s="27"/>
+    <row r="117" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A117" s="29"/>
       <c r="B117" s="3" t="b">
         <v>0</v>
       </c>
@@ -4420,8 +4432,8 @@
       </c>
       <c r="I117" s="3"/>
     </row>
-    <row r="118" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A118" s="27"/>
+    <row r="118" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A118" s="29"/>
       <c r="B118" s="3" t="b">
         <v>0</v>
       </c>
@@ -4445,8 +4457,8 @@
       </c>
       <c r="I118" s="3"/>
     </row>
-    <row r="119" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A119" s="27"/>
+    <row r="119" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A119" s="29"/>
       <c r="B119" s="3" t="b">
         <v>0</v>
       </c>
@@ -4471,7 +4483,7 @@
       <c r="I119" s="3"/>
     </row>
     <row r="120" spans="1:9" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A120" s="27"/>
+      <c r="A120" s="29"/>
       <c r="B120" s="3" t="b">
         <v>0</v>
       </c>
@@ -4494,7 +4506,7 @@
       <c r="I120" s="3"/>
     </row>
     <row r="121" spans="1:9" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A121" s="27"/>
+      <c r="A121" s="29"/>
       <c r="B121" s="3" t="b">
         <v>0</v>
       </c>
@@ -4519,7 +4531,7 @@
       <c r="I121" s="3"/>
     </row>
     <row r="122" spans="1:9" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A122" s="27"/>
+      <c r="A122" s="29"/>
       <c r="B122" s="3" t="b">
         <v>0</v>
       </c>
@@ -4543,8 +4555,8 @@
       </c>
       <c r="I122" s="3"/>
     </row>
-    <row r="123" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A123" s="27"/>
+    <row r="123" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A123" s="29"/>
       <c r="B123" s="3" t="b">
         <v>0</v>
       </c>
@@ -4566,8 +4578,8 @@
       </c>
       <c r="I123" s="3"/>
     </row>
-    <row r="124" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A124" s="27"/>
+    <row r="124" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A124" s="29"/>
       <c r="B124" s="3" t="b">
         <v>0</v>
       </c>
@@ -4589,8 +4601,8 @@
       </c>
       <c r="I124" s="3"/>
     </row>
-    <row r="125" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A125" s="27"/>
+    <row r="125" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A125" s="29"/>
       <c r="B125" s="3" t="b">
         <v>0</v>
       </c>
@@ -4634,8 +4646,8 @@
       <c r="H127" s="21"/>
       <c r="I127" s="3"/>
     </row>
-    <row r="128" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A128" s="26" t="s">
+    <row r="128" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A128" s="32" t="s">
         <v>226</v>
       </c>
       <c r="B128" s="3" t="b">
@@ -4660,7 +4672,7 @@
       <c r="I128" s="3"/>
     </row>
     <row r="129" spans="1:9" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A129" s="27"/>
+      <c r="A129" s="29"/>
       <c r="B129" s="3" t="b">
         <v>0</v>
       </c>
@@ -4684,8 +4696,8 @@
       </c>
       <c r="I129" s="3"/>
     </row>
-    <row r="130" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A130" s="27"/>
+    <row r="130" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A130" s="29"/>
       <c r="B130" s="3" t="b">
         <v>0</v>
       </c>
@@ -4709,8 +4721,8 @@
       </c>
       <c r="I130" s="3"/>
     </row>
-    <row r="131" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A131" s="27"/>
+    <row r="131" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A131" s="29"/>
       <c r="B131" s="3" t="b">
         <v>0</v>
       </c>
@@ -4734,8 +4746,8 @@
       </c>
       <c r="I131" s="3"/>
     </row>
-    <row r="132" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A132" s="27"/>
+    <row r="132" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A132" s="29"/>
       <c r="B132" s="3" t="b">
         <v>0</v>
       </c>
@@ -4760,7 +4772,7 @@
       <c r="I132" s="3"/>
     </row>
     <row r="133" spans="1:9" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A133" s="27"/>
+      <c r="A133" s="29"/>
       <c r="B133" s="3" t="b">
         <v>0</v>
       </c>
@@ -4785,7 +4797,7 @@
       <c r="I133" s="3"/>
     </row>
     <row r="134" spans="1:9" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A134" s="27"/>
+      <c r="A134" s="29"/>
       <c r="B134" s="3" t="b">
         <v>0</v>
       </c>
@@ -4809,8 +4821,8 @@
       </c>
       <c r="I134" s="3"/>
     </row>
-    <row r="135" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A135" s="27"/>
+    <row r="135" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A135" s="29"/>
       <c r="B135" s="3" t="b">
         <v>0</v>
       </c>
@@ -4835,7 +4847,7 @@
       <c r="I135" s="3"/>
     </row>
     <row r="136" spans="1:9" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A136" s="27"/>
+      <c r="A136" s="29"/>
       <c r="B136" s="3" t="b">
         <v>0</v>
       </c>
@@ -4859,8 +4871,8 @@
       </c>
       <c r="I136" s="3"/>
     </row>
-    <row r="137" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A137" s="27"/>
+    <row r="137" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A137" s="29"/>
       <c r="B137" s="3" t="b">
         <v>0</v>
       </c>
@@ -4882,8 +4894,8 @@
       </c>
       <c r="I137" s="3"/>
     </row>
-    <row r="138" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A138" s="27"/>
+    <row r="138" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A138" s="29"/>
       <c r="B138" s="3" t="b">
         <v>0</v>
       </c>
@@ -4907,8 +4919,8 @@
       </c>
       <c r="I138" s="3"/>
     </row>
-    <row r="139" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A139" s="27"/>
+    <row r="139" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A139" s="29"/>
       <c r="B139" s="3" t="b">
         <v>0</v>
       </c>
@@ -4933,7 +4945,7 @@
       <c r="I139" s="3"/>
     </row>
     <row r="140" spans="1:9" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A140" s="27"/>
+      <c r="A140" s="29"/>
       <c r="B140" s="3" t="b">
         <v>0</v>
       </c>
@@ -4958,7 +4970,7 @@
       <c r="I140" s="3"/>
     </row>
     <row r="141" spans="1:9" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A141" s="27"/>
+      <c r="A141" s="29"/>
       <c r="B141" s="3" t="b">
         <v>0</v>
       </c>
@@ -4980,8 +4992,8 @@
       </c>
       <c r="I141" s="3"/>
     </row>
-    <row r="142" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A142" s="27"/>
+    <row r="142" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A142" s="29"/>
       <c r="B142" s="3" t="b">
         <v>0</v>
       </c>
@@ -5027,8 +5039,8 @@
       <c r="H144" s="21"/>
       <c r="I144" s="3"/>
     </row>
-    <row r="145" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A145" s="26" t="s">
+    <row r="145" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A145" s="32" t="s">
         <v>257</v>
       </c>
       <c r="B145" s="3" t="b">
@@ -5052,8 +5064,8 @@
       </c>
       <c r="I145" s="3"/>
     </row>
-    <row r="146" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A146" s="27"/>
+    <row r="146" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A146" s="29"/>
       <c r="B146" s="3" t="b">
         <v>0</v>
       </c>
@@ -5075,8 +5087,8 @@
       </c>
       <c r="I146" s="3"/>
     </row>
-    <row r="147" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A147" s="27"/>
+    <row r="147" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A147" s="29"/>
       <c r="B147" s="3" t="b">
         <v>0</v>
       </c>
@@ -5098,8 +5110,8 @@
       </c>
       <c r="I147" s="3"/>
     </row>
-    <row r="148" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A148" s="27"/>
+    <row r="148" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A148" s="29"/>
       <c r="B148" s="3" t="b">
         <v>0</v>
       </c>
@@ -5121,8 +5133,8 @@
       </c>
       <c r="I148" s="3"/>
     </row>
-    <row r="149" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A149" s="27"/>
+    <row r="149" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A149" s="29"/>
       <c r="B149" s="3" t="b">
         <v>0</v>
       </c>
@@ -5145,7 +5157,7 @@
       <c r="I149" s="3"/>
     </row>
     <row r="150" spans="1:9" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A150" s="27"/>
+      <c r="A150" s="29"/>
       <c r="B150" s="3" t="b">
         <v>0</v>
       </c>
@@ -5189,8 +5201,8 @@
       <c r="H152" s="21"/>
       <c r="I152" s="3"/>
     </row>
-    <row r="153" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A153" s="26" t="s">
+    <row r="153" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A153" s="32" t="s">
         <v>276</v>
       </c>
       <c r="B153" s="3" t="b">
@@ -5214,8 +5226,8 @@
       </c>
       <c r="I153" s="3"/>
     </row>
-    <row r="154" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A154" s="27"/>
+    <row r="154" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A154" s="29"/>
       <c r="B154" s="3" t="b">
         <v>0</v>
       </c>
@@ -5238,7 +5250,7 @@
       <c r="I154" s="3"/>
     </row>
     <row r="155" spans="1:9" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A155" s="27"/>
+      <c r="A155" s="29"/>
       <c r="B155" s="3" t="b">
         <v>0</v>
       </c>
@@ -5260,8 +5272,8 @@
       </c>
       <c r="I155" s="3"/>
     </row>
-    <row r="156" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A156" s="27"/>
+    <row r="156" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A156" s="29"/>
       <c r="B156" s="3" t="b">
         <v>0</v>
       </c>
@@ -5284,7 +5296,7 @@
       <c r="I156" s="3"/>
     </row>
     <row r="157" spans="1:9" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A157" s="27"/>
+      <c r="A157" s="29"/>
       <c r="B157" s="3" t="b">
         <v>0</v>
       </c>
@@ -5328,8 +5340,8 @@
       <c r="H159" s="21"/>
       <c r="I159" s="3"/>
     </row>
-    <row r="160" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A160" s="26" t="s">
+    <row r="160" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A160" s="32" t="s">
         <v>290</v>
       </c>
       <c r="B160" s="3" t="b">
@@ -5353,8 +5365,8 @@
       </c>
       <c r="I160" s="3"/>
     </row>
-    <row r="161" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A161" s="27"/>
+    <row r="161" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A161" s="29"/>
       <c r="B161" s="3" t="b">
         <v>0</v>
       </c>
@@ -5378,8 +5390,8 @@
       </c>
       <c r="I161" s="3"/>
     </row>
-    <row r="162" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A162" s="27"/>
+    <row r="162" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A162" s="29"/>
       <c r="B162" s="3" t="b">
         <v>0</v>
       </c>
@@ -5403,8 +5415,8 @@
       </c>
       <c r="I162" s="3"/>
     </row>
-    <row r="163" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A163" s="27"/>
+    <row r="163" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A163" s="29"/>
       <c r="B163" s="3" t="b">
         <v>0</v>
       </c>
@@ -5426,8 +5438,8 @@
       </c>
       <c r="I163" s="3"/>
     </row>
-    <row r="164" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A164" s="27"/>
+    <row r="164" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A164" s="29"/>
       <c r="B164" s="3" t="b">
         <v>0</v>
       </c>
@@ -5449,8 +5461,8 @@
       </c>
       <c r="I164" s="3"/>
     </row>
-    <row r="165" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A165" s="27"/>
+    <row r="165" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A165" s="29"/>
       <c r="B165" s="3" t="b">
         <v>0</v>
       </c>
@@ -5472,8 +5484,8 @@
       </c>
       <c r="I165" s="3"/>
     </row>
-    <row r="166" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A166" s="27"/>
+    <row r="166" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A166" s="29"/>
       <c r="B166" s="3" t="b">
         <v>0</v>
       </c>
@@ -5495,8 +5507,8 @@
       </c>
       <c r="I166" s="3"/>
     </row>
-    <row r="167" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A167" s="27"/>
+    <row r="167" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A167" s="29"/>
       <c r="B167" s="3" t="b">
         <v>0</v>
       </c>
@@ -5518,8 +5530,8 @@
       </c>
       <c r="I167" s="3"/>
     </row>
-    <row r="168" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A168" s="27"/>
+    <row r="168" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A168" s="29"/>
       <c r="B168" s="3" t="b">
         <v>0</v>
       </c>
@@ -5542,7 +5554,7 @@
       <c r="I168" s="3"/>
     </row>
     <row r="169" spans="1:9" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A169" s="27"/>
+      <c r="A169" s="29"/>
       <c r="B169" s="3" t="b">
         <v>0</v>
       </c>
@@ -5564,8 +5576,8 @@
       </c>
       <c r="I169" s="3"/>
     </row>
-    <row r="170" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A170" s="27"/>
+    <row r="170" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A170" s="29"/>
       <c r="B170" s="3" t="b">
         <v>0</v>
       </c>
@@ -5587,8 +5599,8 @@
       </c>
       <c r="I170" s="3"/>
     </row>
-    <row r="171" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A171" s="27"/>
+    <row r="171" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A171" s="29"/>
       <c r="B171" s="3" t="b">
         <v>0</v>
       </c>
@@ -5610,8 +5622,8 @@
       </c>
       <c r="I171" s="3"/>
     </row>
-    <row r="172" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A172" s="27"/>
+    <row r="172" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A172" s="29"/>
       <c r="B172" s="3" t="b">
         <v>0</v>
       </c>
@@ -5633,8 +5645,8 @@
       </c>
       <c r="I172" s="3"/>
     </row>
-    <row r="173" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A173" s="27"/>
+    <row r="173" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A173" s="29"/>
       <c r="B173" s="3" t="b">
         <v>0</v>
       </c>
@@ -5656,8 +5668,8 @@
       </c>
       <c r="I173" s="3"/>
     </row>
-    <row r="174" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A174" s="27"/>
+    <row r="174" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A174" s="29"/>
       <c r="B174" s="3" t="b">
         <v>0</v>
       </c>
@@ -5679,8 +5691,8 @@
       </c>
       <c r="I174" s="3"/>
     </row>
-    <row r="175" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A175" s="27"/>
+    <row r="175" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A175" s="29"/>
       <c r="B175" s="3" t="b">
         <v>0</v>
       </c>
@@ -5702,8 +5714,8 @@
       </c>
       <c r="I175" s="3"/>
     </row>
-    <row r="176" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A176" s="27"/>
+    <row r="176" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A176" s="29"/>
       <c r="B176" s="3" t="b">
         <v>0</v>
       </c>
@@ -5726,7 +5738,7 @@
       <c r="I176" s="3"/>
     </row>
     <row r="177" spans="1:9" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A177" s="27"/>
+      <c r="A177" s="29"/>
       <c r="B177" s="3" t="b">
         <v>0</v>
       </c>
@@ -5748,8 +5760,8 @@
       </c>
       <c r="I177" s="3"/>
     </row>
-    <row r="178" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A178" s="27"/>
+    <row r="178" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A178" s="29"/>
       <c r="B178" s="3" t="b">
         <v>0</v>
       </c>
@@ -5771,8 +5783,8 @@
       </c>
       <c r="I178" s="3"/>
     </row>
-    <row r="179" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A179" s="27"/>
+    <row r="179" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A179" s="29"/>
       <c r="B179" s="3" t="b">
         <v>0</v>
       </c>
@@ -5794,8 +5806,8 @@
       </c>
       <c r="I179" s="3"/>
     </row>
-    <row r="180" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A180" s="27"/>
+    <row r="180" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A180" s="29"/>
       <c r="B180" s="3" t="b">
         <v>0</v>
       </c>
@@ -5817,8 +5829,8 @@
       </c>
       <c r="I180" s="3"/>
     </row>
-    <row r="181" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A181" s="27"/>
+    <row r="181" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A181" s="29"/>
       <c r="B181" s="3" t="b">
         <v>0</v>
       </c>
@@ -5841,7 +5853,7 @@
       <c r="I181" s="3"/>
     </row>
     <row r="182" spans="1:9" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A182" s="27"/>
+      <c r="A182" s="29"/>
       <c r="B182" s="3" t="b">
         <v>0</v>
       </c>
@@ -5864,7 +5876,7 @@
       <c r="I182" s="3"/>
     </row>
     <row r="183" spans="1:9" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A183" s="27"/>
+      <c r="A183" s="29"/>
       <c r="B183" s="3" t="b">
         <v>0</v>
       </c>
@@ -5887,7 +5899,7 @@
       <c r="I183" s="3"/>
     </row>
     <row r="184" spans="1:9" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A184" s="27"/>
+      <c r="A184" s="29"/>
       <c r="B184" s="3" t="b">
         <v>0</v>
       </c>
@@ -5909,8 +5921,8 @@
       </c>
       <c r="I184" s="3"/>
     </row>
-    <row r="185" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A185" s="27"/>
+    <row r="185" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A185" s="29"/>
       <c r="B185" s="3" t="b">
         <v>0</v>
       </c>
@@ -5954,8 +5966,8 @@
       <c r="H187" s="21"/>
       <c r="I187" s="3"/>
     </row>
-    <row r="188" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A188" s="26" t="s">
+    <row r="188" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A188" s="32" t="s">
         <v>362</v>
       </c>
       <c r="B188" s="3" t="b">
@@ -5979,8 +5991,8 @@
       </c>
       <c r="I188" s="3"/>
     </row>
-    <row r="189" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A189" s="27"/>
+    <row r="189" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A189" s="29"/>
       <c r="B189" s="3" t="b">
         <v>0</v>
       </c>
@@ -6003,7 +6015,7 @@
       <c r="I189" s="3"/>
     </row>
     <row r="190" spans="1:9" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A190" s="27"/>
+      <c r="A190" s="29"/>
       <c r="B190" s="3" t="b">
         <v>0</v>
       </c>
@@ -6026,7 +6038,7 @@
       <c r="I190" s="3"/>
     </row>
     <row r="191" spans="1:9" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A191" s="27"/>
+      <c r="A191" s="29"/>
       <c r="B191" s="3" t="b">
         <v>0</v>
       </c>
@@ -6048,8 +6060,8 @@
       </c>
       <c r="I191" s="3"/>
     </row>
-    <row r="192" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A192" s="27"/>
+    <row r="192" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A192" s="29"/>
       <c r="B192" s="3" t="b">
         <v>0</v>
       </c>
@@ -6071,8 +6083,8 @@
       </c>
       <c r="I192" s="3"/>
     </row>
-    <row r="193" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A193" s="27"/>
+    <row r="193" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A193" s="29"/>
       <c r="B193" s="3" t="b">
         <v>0</v>
       </c>
@@ -6094,8 +6106,8 @@
       </c>
       <c r="I193" s="3"/>
     </row>
-    <row r="194" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A194" s="27"/>
+    <row r="194" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A194" s="29"/>
       <c r="B194" s="3" t="b">
         <v>0</v>
       </c>
@@ -6118,7 +6130,7 @@
       <c r="I194" s="3"/>
     </row>
     <row r="195" spans="1:9" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A195" s="27"/>
+      <c r="A195" s="29"/>
       <c r="B195" s="3" t="b">
         <v>0</v>
       </c>
@@ -6140,8 +6152,8 @@
       </c>
       <c r="I195" s="3"/>
     </row>
-    <row r="196" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A196" s="27"/>
+    <row r="196" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A196" s="29"/>
       <c r="B196" s="3" t="b">
         <v>0</v>
       </c>
@@ -6163,8 +6175,8 @@
       </c>
       <c r="I196" s="3"/>
     </row>
-    <row r="197" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A197" s="27"/>
+    <row r="197" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A197" s="29"/>
       <c r="B197" s="3" t="b">
         <v>0</v>
       </c>
@@ -6187,7 +6199,7 @@
       <c r="I197" s="3"/>
     </row>
     <row r="198" spans="1:9" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A198" s="27"/>
+      <c r="A198" s="29"/>
       <c r="B198" s="3" t="b">
         <v>0</v>
       </c>
@@ -6209,8 +6221,8 @@
       </c>
       <c r="I198" s="3"/>
     </row>
-    <row r="199" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A199" s="27"/>
+    <row r="199" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A199" s="29"/>
       <c r="B199" s="3" t="b">
         <v>0</v>
       </c>
@@ -6232,8 +6244,8 @@
       </c>
       <c r="I199" s="3"/>
     </row>
-    <row r="200" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A200" s="27"/>
+    <row r="200" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A200" s="29"/>
       <c r="B200" s="3" t="b">
         <v>0</v>
       </c>
@@ -6255,8 +6267,8 @@
       </c>
       <c r="I200" s="3"/>
     </row>
-    <row r="201" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A201" s="27"/>
+    <row r="201" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A201" s="29"/>
       <c r="B201" s="3" t="b">
         <v>0</v>
       </c>
@@ -6279,7 +6291,7 @@
       <c r="I201" s="3"/>
     </row>
     <row r="202" spans="1:9" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A202" s="27"/>
+      <c r="A202" s="29"/>
       <c r="B202" s="3" t="b">
         <v>0</v>
       </c>
@@ -6302,7 +6314,7 @@
       <c r="I202" s="3"/>
     </row>
     <row r="203" spans="1:9" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A203" s="27"/>
+      <c r="A203" s="29"/>
       <c r="B203" s="3" t="b">
         <v>0</v>
       </c>
@@ -6325,7 +6337,7 @@
       <c r="I203" s="3"/>
     </row>
     <row r="204" spans="1:9" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A204" s="27"/>
+      <c r="A204" s="29"/>
       <c r="B204" s="3" t="b">
         <v>0</v>
       </c>
@@ -6348,7 +6360,7 @@
       <c r="I204" s="3"/>
     </row>
     <row r="205" spans="1:9" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A205" s="27"/>
+      <c r="A205" s="29"/>
       <c r="B205" s="3" t="b">
         <v>0</v>
       </c>
@@ -6370,8 +6382,8 @@
       </c>
       <c r="I205" s="3"/>
     </row>
-    <row r="206" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A206" s="27"/>
+    <row r="206" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A206" s="29"/>
       <c r="B206" s="3" t="b">
         <v>0</v>
       </c>
@@ -6393,8 +6405,8 @@
       </c>
       <c r="I206" s="3"/>
     </row>
-    <row r="207" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A207" s="27"/>
+    <row r="207" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A207" s="29"/>
       <c r="B207" s="3" t="b">
         <v>0</v>
       </c>
@@ -6417,7 +6429,7 @@
       <c r="I207" s="3"/>
     </row>
     <row r="208" spans="1:9" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A208" s="27"/>
+      <c r="A208" s="29"/>
       <c r="B208" s="3" t="b">
         <v>0</v>
       </c>
@@ -6462,7 +6474,7 @@
       <c r="I210" s="3"/>
     </row>
     <row r="211" spans="1:9" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A211" s="26" t="s">
+      <c r="A211" s="32" t="s">
         <v>405</v>
       </c>
       <c r="B211" s="3" t="b">
@@ -6486,8 +6498,8 @@
       </c>
       <c r="I211" s="3"/>
     </row>
-    <row r="212" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A212" s="27"/>
+    <row r="212" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A212" s="29"/>
       <c r="B212" s="3" t="b">
         <v>0</v>
       </c>
@@ -6509,8 +6521,8 @@
       </c>
       <c r="I212" s="3"/>
     </row>
-    <row r="213" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A213" s="27"/>
+    <row r="213" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A213" s="29"/>
       <c r="B213" s="3" t="b">
         <v>0</v>
       </c>
@@ -6532,8 +6544,8 @@
       </c>
       <c r="I213" s="3"/>
     </row>
-    <row r="214" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A214" s="27"/>
+    <row r="214" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A214" s="29"/>
       <c r="B214" s="3" t="b">
         <v>0</v>
       </c>
@@ -6555,8 +6567,8 @@
       </c>
       <c r="I214" s="3"/>
     </row>
-    <row r="215" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A215" s="27"/>
+    <row r="215" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A215" s="29"/>
       <c r="B215" s="3" t="b">
         <v>0</v>
       </c>
@@ -6578,8 +6590,8 @@
       </c>
       <c r="I215" s="3"/>
     </row>
-    <row r="216" spans="1:9" ht="13" x14ac:dyDescent="0.3">
-      <c r="A216" s="27"/>
+    <row r="216" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
+      <c r="A216" s="29"/>
       <c r="B216" s="3" t="b">
         <v>0</v>
       </c>
@@ -15249,11 +15261,6 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="D1:F1"/>
-    <mergeCell ref="D2:F2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="A6:A32"/>
-    <mergeCell ref="A35:A41"/>
     <mergeCell ref="A44:A54"/>
     <mergeCell ref="A57:A67"/>
     <mergeCell ref="A188:A208"/>
@@ -15265,6 +15272,11 @@
     <mergeCell ref="A145:A150"/>
     <mergeCell ref="A153:A157"/>
     <mergeCell ref="A160:A185"/>
+    <mergeCell ref="D1:F1"/>
+    <mergeCell ref="D2:F2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="A6:A32"/>
+    <mergeCell ref="A35:A41"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>

--- a/DSA for PLACEMENTS 1.xlsx
+++ b/DSA for PLACEMENTS 1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9765abdd1e291f17/Desktop/DSA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="11_2E2C462B86E80A008A522AE716C952C441A6BCAD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B004C84D-FC14-48E7-A0E3-EFE78325CDA3}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="11_2E2C462B86E80A008A522AE716C952C441A6BCAD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6C477E00-8E0D-439C-8DE7-BC490CEC3492}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="856" uniqueCount="421">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="858" uniqueCount="421">
   <si>
     <t>Do NOT send any edit request to this sheet. Instead, make a copy of your own.</t>
   </si>
@@ -1534,21 +1534,21 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1786,7 +1786,7 @@
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="2"/>
-      <c r="D1" s="28" t="s">
+      <c r="D1" s="31" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="29"/>
@@ -1799,13 +1799,13 @@
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="2"/>
-      <c r="D2" s="30" t="s">
+      <c r="D2" s="32" t="s">
         <v>1</v>
       </c>
       <c r="E2" s="29"/>
       <c r="F2" s="29"/>
       <c r="G2" s="3"/>
-      <c r="H2" s="31" t="s">
+      <c r="H2" s="33" t="s">
         <v>2</v>
       </c>
       <c r="I2" s="29"/>
@@ -1861,7 +1861,7 @@
       <c r="I5" s="3"/>
     </row>
     <row r="6" spans="1:10" ht="14.5" x14ac:dyDescent="0.4">
-      <c r="A6" s="32" t="s">
+      <c r="A6" s="28" t="s">
         <v>10</v>
       </c>
       <c r="B6" s="3" t="b">
@@ -2065,6 +2065,9 @@
       </c>
       <c r="H13" s="9"/>
       <c r="I13" s="3"/>
+      <c r="J13" s="1" t="s">
+        <v>419</v>
+      </c>
     </row>
     <row r="14" spans="1:10" ht="14.5" x14ac:dyDescent="0.4">
       <c r="A14" s="29"/>
@@ -2090,6 +2093,9 @@
         <v>30</v>
       </c>
       <c r="I14" s="3"/>
+      <c r="J14" s="1" t="s">
+        <v>419</v>
+      </c>
     </row>
     <row r="15" spans="1:10" ht="14.5" x14ac:dyDescent="0.4">
       <c r="A15" s="29"/>
@@ -2554,7 +2560,7 @@
       <c r="I34" s="3"/>
     </row>
     <row r="35" spans="1:9" ht="15" x14ac:dyDescent="0.4">
-      <c r="A35" s="33" t="s">
+      <c r="A35" s="30" t="s">
         <v>68</v>
       </c>
       <c r="B35" s="3" t="b">
@@ -2745,7 +2751,7 @@
       <c r="I43" s="3"/>
     </row>
     <row r="44" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
-      <c r="A44" s="32" t="s">
+      <c r="A44" s="28" t="s">
         <v>80</v>
       </c>
       <c r="B44" s="3" t="b">
@@ -3018,7 +3024,7 @@
       <c r="I56" s="3"/>
     </row>
     <row r="57" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
-      <c r="A57" s="33" t="s">
+      <c r="A57" s="30" t="s">
         <v>98</v>
       </c>
       <c r="B57" s="3" t="b">
@@ -3307,7 +3313,7 @@
       <c r="I69" s="3"/>
     </row>
     <row r="70" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
-      <c r="A70" s="33" t="s">
+      <c r="A70" s="30" t="s">
         <v>118</v>
       </c>
       <c r="B70" s="3" t="b">
@@ -3648,7 +3654,7 @@
       <c r="I84" s="3"/>
     </row>
     <row r="85" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
-      <c r="A85" s="32" t="s">
+      <c r="A85" s="28" t="s">
         <v>145</v>
       </c>
       <c r="B85" s="3" t="b">
@@ -4041,7 +4047,7 @@
       <c r="I101" s="3"/>
     </row>
     <row r="102" spans="1:9" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A102" s="32" t="s">
+      <c r="A102" s="28" t="s">
         <v>176</v>
       </c>
       <c r="B102" s="3" t="b">
@@ -4647,7 +4653,7 @@
       <c r="I127" s="3"/>
     </row>
     <row r="128" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
-      <c r="A128" s="32" t="s">
+      <c r="A128" s="28" t="s">
         <v>226</v>
       </c>
       <c r="B128" s="3" t="b">
@@ -5040,7 +5046,7 @@
       <c r="I144" s="3"/>
     </row>
     <row r="145" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
-      <c r="A145" s="32" t="s">
+      <c r="A145" s="28" t="s">
         <v>257</v>
       </c>
       <c r="B145" s="3" t="b">
@@ -5202,7 +5208,7 @@
       <c r="I152" s="3"/>
     </row>
     <row r="153" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
-      <c r="A153" s="32" t="s">
+      <c r="A153" s="28" t="s">
         <v>276</v>
       </c>
       <c r="B153" s="3" t="b">
@@ -5341,7 +5347,7 @@
       <c r="I159" s="3"/>
     </row>
     <row r="160" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
-      <c r="A160" s="32" t="s">
+      <c r="A160" s="28" t="s">
         <v>290</v>
       </c>
       <c r="B160" s="3" t="b">
@@ -5967,7 +5973,7 @@
       <c r="I187" s="3"/>
     </row>
     <row r="188" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
-      <c r="A188" s="32" t="s">
+      <c r="A188" s="28" t="s">
         <v>362</v>
       </c>
       <c r="B188" s="3" t="b">
@@ -6474,7 +6480,7 @@
       <c r="I210" s="3"/>
     </row>
     <row r="211" spans="1:9" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A211" s="32" t="s">
+      <c r="A211" s="28" t="s">
         <v>405</v>
       </c>
       <c r="B211" s="3" t="b">
@@ -15261,6 +15267,11 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="D1:F1"/>
+    <mergeCell ref="D2:F2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="A6:A32"/>
+    <mergeCell ref="A35:A41"/>
     <mergeCell ref="A44:A54"/>
     <mergeCell ref="A57:A67"/>
     <mergeCell ref="A188:A208"/>
@@ -15272,11 +15283,6 @@
     <mergeCell ref="A145:A150"/>
     <mergeCell ref="A153:A157"/>
     <mergeCell ref="A160:A185"/>
-    <mergeCell ref="D1:F1"/>
-    <mergeCell ref="D2:F2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="A6:A32"/>
-    <mergeCell ref="A35:A41"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>

--- a/DSA for PLACEMENTS 1.xlsx
+++ b/DSA for PLACEMENTS 1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9765abdd1e291f17/Desktop/DSA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="11_2E2C462B86E80A008A522AE716C952C441A6BCAD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6C477E00-8E0D-439C-8DE7-BC490CEC3492}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="11_2E2C462B86E80A008A522AE716C952C441A6BCAD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FA5879A7-621F-4421-B3F3-F2B2589B2B4A}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="858" uniqueCount="421">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="859" uniqueCount="421">
   <si>
     <t>Do NOT send any edit request to this sheet. Instead, make a copy of your own.</t>
   </si>
@@ -1534,21 +1534,21 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1786,7 +1786,7 @@
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="2"/>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="28" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="29"/>
@@ -1799,13 +1799,13 @@
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="2"/>
-      <c r="D2" s="32" t="s">
+      <c r="D2" s="30" t="s">
         <v>1</v>
       </c>
       <c r="E2" s="29"/>
       <c r="F2" s="29"/>
       <c r="G2" s="3"/>
-      <c r="H2" s="33" t="s">
+      <c r="H2" s="31" t="s">
         <v>2</v>
       </c>
       <c r="I2" s="29"/>
@@ -1861,7 +1861,7 @@
       <c r="I5" s="3"/>
     </row>
     <row r="6" spans="1:10" ht="14.5" x14ac:dyDescent="0.4">
-      <c r="A6" s="28" t="s">
+      <c r="A6" s="32" t="s">
         <v>10</v>
       </c>
       <c r="B6" s="3" t="b">
@@ -2123,6 +2123,9 @@
       <c r="I15" s="3" t="s">
         <v>21</v>
       </c>
+      <c r="J15" s="1" t="s">
+        <v>419</v>
+      </c>
     </row>
     <row r="16" spans="1:10" ht="14.5" x14ac:dyDescent="0.4">
       <c r="A16" s="29"/>
@@ -2560,7 +2563,7 @@
       <c r="I34" s="3"/>
     </row>
     <row r="35" spans="1:9" ht="15" x14ac:dyDescent="0.4">
-      <c r="A35" s="30" t="s">
+      <c r="A35" s="33" t="s">
         <v>68</v>
       </c>
       <c r="B35" s="3" t="b">
@@ -2751,7 +2754,7 @@
       <c r="I43" s="3"/>
     </row>
     <row r="44" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
-      <c r="A44" s="28" t="s">
+      <c r="A44" s="32" t="s">
         <v>80</v>
       </c>
       <c r="B44" s="3" t="b">
@@ -3024,7 +3027,7 @@
       <c r="I56" s="3"/>
     </row>
     <row r="57" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
-      <c r="A57" s="30" t="s">
+      <c r="A57" s="33" t="s">
         <v>98</v>
       </c>
       <c r="B57" s="3" t="b">
@@ -3313,7 +3316,7 @@
       <c r="I69" s="3"/>
     </row>
     <row r="70" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
-      <c r="A70" s="30" t="s">
+      <c r="A70" s="33" t="s">
         <v>118</v>
       </c>
       <c r="B70" s="3" t="b">
@@ -3654,7 +3657,7 @@
       <c r="I84" s="3"/>
     </row>
     <row r="85" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
-      <c r="A85" s="28" t="s">
+      <c r="A85" s="32" t="s">
         <v>145</v>
       </c>
       <c r="B85" s="3" t="b">
@@ -4047,7 +4050,7 @@
       <c r="I101" s="3"/>
     </row>
     <row r="102" spans="1:9" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A102" s="28" t="s">
+      <c r="A102" s="32" t="s">
         <v>176</v>
       </c>
       <c r="B102" s="3" t="b">
@@ -4653,7 +4656,7 @@
       <c r="I127" s="3"/>
     </row>
     <row r="128" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
-      <c r="A128" s="28" t="s">
+      <c r="A128" s="32" t="s">
         <v>226</v>
       </c>
       <c r="B128" s="3" t="b">
@@ -5046,7 +5049,7 @@
       <c r="I144" s="3"/>
     </row>
     <row r="145" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
-      <c r="A145" s="28" t="s">
+      <c r="A145" s="32" t="s">
         <v>257</v>
       </c>
       <c r="B145" s="3" t="b">
@@ -5208,7 +5211,7 @@
       <c r="I152" s="3"/>
     </row>
     <row r="153" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
-      <c r="A153" s="28" t="s">
+      <c r="A153" s="32" t="s">
         <v>276</v>
       </c>
       <c r="B153" s="3" t="b">
@@ -5347,7 +5350,7 @@
       <c r="I159" s="3"/>
     </row>
     <row r="160" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
-      <c r="A160" s="28" t="s">
+      <c r="A160" s="32" t="s">
         <v>290</v>
       </c>
       <c r="B160" s="3" t="b">
@@ -5973,7 +5976,7 @@
       <c r="I187" s="3"/>
     </row>
     <row r="188" spans="1:9" ht="14.5" x14ac:dyDescent="0.4">
-      <c r="A188" s="28" t="s">
+      <c r="A188" s="32" t="s">
         <v>362</v>
       </c>
       <c r="B188" s="3" t="b">
@@ -6480,7 +6483,7 @@
       <c r="I210" s="3"/>
     </row>
     <row r="211" spans="1:9" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A211" s="28" t="s">
+      <c r="A211" s="32" t="s">
         <v>405</v>
       </c>
       <c r="B211" s="3" t="b">
@@ -15267,11 +15270,6 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="D1:F1"/>
-    <mergeCell ref="D2:F2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="A6:A32"/>
-    <mergeCell ref="A35:A41"/>
     <mergeCell ref="A44:A54"/>
     <mergeCell ref="A57:A67"/>
     <mergeCell ref="A188:A208"/>
@@ -15283,6 +15281,11 @@
     <mergeCell ref="A145:A150"/>
     <mergeCell ref="A153:A157"/>
     <mergeCell ref="A160:A185"/>
+    <mergeCell ref="D1:F1"/>
+    <mergeCell ref="D2:F2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="A6:A32"/>
+    <mergeCell ref="A35:A41"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
